--- a/data/trans_dic/P25C$pormicuenta_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,12; 93,91</t>
+          <t>86,19; 93,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,19; 98,16</t>
+          <t>85,94; 97,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,33; 94,14</t>
+          <t>87,28; 94,02</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,44; 98,4</t>
+          <t>89,1; 98,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,78; 92,99</t>
+          <t>86,3; 93,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,56; 97,58</t>
+          <t>89,7; 97,49</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,52; 91,16</t>
+          <t>78,86; 91,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,98; 92,79</t>
+          <t>81,27; 92,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,71; 90,75</t>
+          <t>82,3; 90,95</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,54; 96,9</t>
+          <t>88,68; 96,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,18; 92,37</t>
+          <t>87,1; 92,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,06; 95,8</t>
+          <t>89,06; 95,59</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>142731; 155640</t>
+          <t>142857; 155553</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38660; 43525</t>
+          <t>38104; 43364</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183453; 197775</t>
+          <t>183357; 197515</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>486898; 535688</t>
+          <t>485064; 535658</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>176272; 188888</t>
+          <t>175288; 188896</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>669482; 729465</t>
+          <t>670550; 728784</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>107831; 125193</t>
+          <t>108300; 125838</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70524; 80814</t>
+          <t>70781; 80472</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>183379; 203677</t>
+          <t>184693; 204120</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>750334; 821221</t>
+          <t>751539; 821625</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>291676; 309013</t>
+          <t>291390; 309803</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1052750; 1132424</t>
+          <t>1052678; 1129955</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$pormicuenta_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Estudios-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,19; 93,85</t>
+          <t>85,56; 93,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,94; 97,8</t>
+          <t>86,84; 98,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,28; 94,02</t>
+          <t>87,43; 93,95</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,1; 98,39</t>
+          <t>87,03; 93,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,3; 93,0</t>
+          <t>86,99; 93,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,7; 97,49</t>
+          <t>87,85; 92,57</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,86; 91,63</t>
+          <t>78,57; 90,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,27; 92,4</t>
+          <t>81,3; 92,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,3; 90,95</t>
+          <t>81,79; 90,67</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,68; 96,95</t>
+          <t>86,73; 91,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,1; 92,6</t>
+          <t>87,69; 92,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,06; 95,59</t>
+          <t>87,82; 91,44</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>149771</t>
+          <t>159165</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>44234</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191403</t>
+          <t>203399</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>142857; 155553</t>
+          <t>150690; 165441</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38104; 43364</t>
+          <t>40862; 46186</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183357; 197515</t>
+          <t>195120; 209669</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>515697</t>
+          <t>300741</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>183274</t>
+          <t>201368</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>698971</t>
+          <t>502109</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>485064; 535658</t>
+          <t>289364; 310777</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>175288; 188896</t>
+          <t>193231; 207561</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>670550; 728784</t>
+          <t>487233; 513410</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>118498</t>
+          <t>127826</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>84028</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195065</t>
+          <t>211855</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>108300; 125838</t>
+          <t>116817; 134969</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>70781; 80472</t>
+          <t>77718; 88506</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184693; 204120</t>
+          <t>199783; 221481</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>783966</t>
+          <t>587732</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>301473</t>
+          <t>329630</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1085439</t>
+          <t>917362</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>751539; 821625</t>
+          <t>570074; 602400</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>291390; 309803</t>
+          <t>319875; 337576</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1052678; 1129955</t>
+          <t>897617; 934561</t>
         </is>
       </c>
     </row>
